--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -5400,7 +5400,7 @@
       <c r="D97" s="7" t="inlineStr">
         <is>
           <t>pos 12
-&amp;none</t>
+&amp;mo MOUSE_SCROLL</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
@@ -5467,7 +5467,11 @@
       </c>
       <c r="B98" s="9" t="inlineStr"/>
       <c r="C98" s="9" t="inlineStr"/>
-      <c r="D98" s="9" t="inlineStr"/>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
       <c r="E98" s="9" t="inlineStr"/>
       <c r="F98" s="9" t="inlineStr"/>
       <c r="G98" s="9" t="inlineStr"/>
@@ -5793,7 +5797,7 @@
       <c r="C106" s="7" t="inlineStr">
         <is>
           <t>pos 11
-&amp;none</t>
+&amp;mkp MB2</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
@@ -5805,7 +5809,7 @@
       <c r="E106" s="7" t="inlineStr">
         <is>
           <t>pos 13
-&amp;none</t>
+&amp;mkp MB1</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
@@ -5865,9 +5869,17 @@
         </is>
       </c>
       <c r="B107" s="9" t="inlineStr"/>
-      <c r="C107" s="9" t="inlineStr"/>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>🖱右</t>
+        </is>
+      </c>
       <c r="D107" s="9" t="inlineStr"/>
-      <c r="E107" s="9" t="inlineStr"/>
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>🖱左</t>
+        </is>
+      </c>
       <c r="F107" s="9" t="inlineStr"/>
       <c r="G107" s="9" t="inlineStr"/>
       <c r="H107" s="9" t="inlineStr"/>
@@ -5901,7 +5913,7 @@
       <c r="C108" s="7" t="inlineStr">
         <is>
           <t>pos 23
-&amp;none</t>
+&amp;mkp MB5</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
@@ -5913,7 +5925,7 @@
       <c r="E108" s="7" t="inlineStr">
         <is>
           <t>pos 25
-&amp;none</t>
+&amp;mkp MB4</t>
         </is>
       </c>
       <c r="F108" s="7" t="inlineStr">
@@ -5973,9 +5985,17 @@
         </is>
       </c>
       <c r="B109" s="9" t="inlineStr"/>
-      <c r="C109" s="9" t="inlineStr"/>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>🖱進</t>
+        </is>
+      </c>
       <c r="D109" s="9" t="inlineStr"/>
-      <c r="E109" s="9" t="inlineStr"/>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>🖱戻</t>
+        </is>
+      </c>
       <c r="F109" s="9" t="inlineStr"/>
       <c r="G109" s="9" t="inlineStr"/>
       <c r="H109" s="9" t="inlineStr"/>
@@ -11016,7 +11036,7 @@
       <c r="D97" s="7" t="inlineStr">
         <is>
           <t>pos 12
-&amp;none</t>
+&amp;mo MOUSE_SCROLL</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
@@ -11083,7 +11103,11 @@
       </c>
       <c r="B98" s="9" t="inlineStr"/>
       <c r="C98" s="9" t="inlineStr"/>
-      <c r="D98" s="9" t="inlineStr"/>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mo MOUSE_SCROLL</t>
+        </is>
+      </c>
       <c r="E98" s="9" t="inlineStr"/>
       <c r="F98" s="9" t="inlineStr"/>
       <c r="G98" s="9" t="inlineStr"/>
@@ -11409,7 +11433,7 @@
       <c r="C106" s="7" t="inlineStr">
         <is>
           <t>pos 11
-&amp;none</t>
+&amp;mkp MB2</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
@@ -11421,7 +11445,7 @@
       <c r="E106" s="7" t="inlineStr">
         <is>
           <t>pos 13
-&amp;none</t>
+&amp;mkp MB1</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
@@ -11481,9 +11505,17 @@
         </is>
       </c>
       <c r="B107" s="9" t="inlineStr"/>
-      <c r="C107" s="9" t="inlineStr"/>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mkp MB2</t>
+        </is>
+      </c>
       <c r="D107" s="9" t="inlineStr"/>
-      <c r="E107" s="9" t="inlineStr"/>
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mkp MB1</t>
+        </is>
+      </c>
       <c r="F107" s="9" t="inlineStr"/>
       <c r="G107" s="9" t="inlineStr"/>
       <c r="H107" s="9" t="inlineStr"/>
@@ -11517,7 +11549,7 @@
       <c r="C108" s="7" t="inlineStr">
         <is>
           <t>pos 23
-&amp;none</t>
+&amp;mkp MB5</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
@@ -11529,7 +11561,7 @@
       <c r="E108" s="7" t="inlineStr">
         <is>
           <t>pos 25
-&amp;none</t>
+&amp;mkp MB4</t>
         </is>
       </c>
       <c r="F108" s="7" t="inlineStr">
@@ -11589,9 +11621,17 @@
         </is>
       </c>
       <c r="B109" s="9" t="inlineStr"/>
-      <c r="C109" s="9" t="inlineStr"/>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mkp MB5</t>
+        </is>
+      </c>
       <c r="D109" s="9" t="inlineStr"/>
-      <c r="E109" s="9" t="inlineStr"/>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mkp MB4</t>
+        </is>
+      </c>
       <c r="F109" s="9" t="inlineStr"/>
       <c r="G109" s="9" t="inlineStr"/>
       <c r="H109" s="9" t="inlineStr"/>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -5388,7 +5388,7 @@
       <c r="B97" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;none</t>
+&amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
@@ -5455,7 +5455,7 @@
       <c r="N97" s="7" t="inlineStr">
         <is>
           <t>pos 21
-&amp;none</t>
+&amp;kp RCTRL</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,11 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B98" s="9" t="inlineStr"/>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t>LCtrl</t>
+        </is>
+      </c>
       <c r="C98" s="9" t="inlineStr"/>
       <c r="D98" s="9" t="inlineStr">
         <is>
@@ -5485,7 +5489,11 @@
         </is>
       </c>
       <c r="M98" s="9" t="inlineStr"/>
-      <c r="N98" s="9" t="inlineStr"/>
+      <c r="N98" s="9" t="inlineStr">
+        <is>
+          <t>RCtrl</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="6" t="inlineStr">
@@ -5496,7 +5504,7 @@
       <c r="B99" s="7" t="inlineStr">
         <is>
           <t>pos 22
-&amp;none</t>
+&amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
@@ -5563,7 +5571,7 @@
       <c r="N99" s="7" t="inlineStr">
         <is>
           <t>pos 33
-&amp;none</t>
+&amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
     </row>
@@ -5573,7 +5581,11 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B100" s="9" t="inlineStr"/>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>LShift</t>
+        </is>
+      </c>
       <c r="C100" s="9" t="inlineStr"/>
       <c r="D100" s="9" t="inlineStr"/>
       <c r="E100" s="9" t="inlineStr"/>
@@ -5585,7 +5597,11 @@
       <c r="K100" s="9" t="inlineStr"/>
       <c r="L100" s="9" t="inlineStr"/>
       <c r="M100" s="9" t="inlineStr"/>
-      <c r="N100" s="9" t="inlineStr"/>
+      <c r="N100" s="9" t="inlineStr">
+        <is>
+          <t>RShift</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="6" t="inlineStr">
@@ -5602,13 +5618,13 @@
       <c r="C101" s="7" t="inlineStr">
         <is>
           <t>pos 35
-&amp;none</t>
+&amp;kp LEFT_WIN</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
           <t>pos 36
-&amp;none</t>
+&amp;kp LEFT_ALT</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
@@ -5659,8 +5675,16 @@
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr"/>
-      <c r="C102" s="9" t="inlineStr"/>
-      <c r="D102" s="9" t="inlineStr"/>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>LWin</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>LAlt</t>
+        </is>
+      </c>
       <c r="E102" s="9" t="inlineStr"/>
       <c r="F102" s="9" t="inlineStr"/>
       <c r="G102" s="9" t="inlineStr"/>
@@ -5791,7 +5815,7 @@
       <c r="B106" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;none</t>
+&amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
@@ -5858,7 +5882,7 @@
       <c r="N106" s="7" t="inlineStr">
         <is>
           <t>pos 21
-&amp;none</t>
+&amp;kp RCTRL</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5892,11 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B107" s="9" t="inlineStr"/>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>LCtrl</t>
+        </is>
+      </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
           <t>🖱右</t>
@@ -5896,7 +5924,11 @@
           <t>🖱右</t>
         </is>
       </c>
-      <c r="N107" s="9" t="inlineStr"/>
+      <c r="N107" s="9" t="inlineStr">
+        <is>
+          <t>RCtrl</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="6" t="inlineStr">
@@ -5907,7 +5939,7 @@
       <c r="B108" s="7" t="inlineStr">
         <is>
           <t>pos 22
-&amp;none</t>
+&amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
@@ -5974,7 +6006,7 @@
       <c r="N108" s="7" t="inlineStr">
         <is>
           <t>pos 33
-&amp;none</t>
+&amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
     </row>
@@ -5984,7 +6016,11 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B109" s="9" t="inlineStr"/>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>LShift</t>
+        </is>
+      </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
           <t>🖱進</t>
@@ -6012,7 +6048,11 @@
           <t>🖱進</t>
         </is>
       </c>
-      <c r="N109" s="9" t="inlineStr"/>
+      <c r="N109" s="9" t="inlineStr">
+        <is>
+          <t>RShift</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="6" t="inlineStr">
@@ -6029,13 +6069,13 @@
       <c r="C110" s="7" t="inlineStr">
         <is>
           <t>pos 35
-&amp;none</t>
+&amp;kp LEFT_WIN</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
           <t>pos 36
-&amp;none</t>
+&amp;kp LEFT_ALT</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
@@ -6086,8 +6126,16 @@
         </is>
       </c>
       <c r="B111" s="9" t="inlineStr"/>
-      <c r="C111" s="9" t="inlineStr"/>
-      <c r="D111" s="9" t="inlineStr"/>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>LWin</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>LAlt</t>
+        </is>
+      </c>
       <c r="E111" s="9" t="inlineStr"/>
       <c r="F111" s="9" t="inlineStr"/>
       <c r="G111" s="9" t="inlineStr"/>
@@ -11024,7 +11072,7 @@
       <c r="B97" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;none</t>
+&amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
@@ -11091,7 +11139,7 @@
       <c r="N97" s="7" t="inlineStr">
         <is>
           <t>pos 21
-&amp;none</t>
+&amp;kp RCTRL</t>
         </is>
       </c>
     </row>
@@ -11101,7 +11149,11 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B98" s="9" t="inlineStr"/>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LCTRL</t>
+        </is>
+      </c>
       <c r="C98" s="9" t="inlineStr"/>
       <c r="D98" s="9" t="inlineStr">
         <is>
@@ -11121,7 +11173,11 @@
         </is>
       </c>
       <c r="M98" s="9" t="inlineStr"/>
-      <c r="N98" s="9" t="inlineStr"/>
+      <c r="N98" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RCTRL</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="6" t="inlineStr">
@@ -11132,7 +11188,7 @@
       <c r="B99" s="7" t="inlineStr">
         <is>
           <t>pos 22
-&amp;none</t>
+&amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
@@ -11199,7 +11255,7 @@
       <c r="N99" s="7" t="inlineStr">
         <is>
           <t>pos 33
-&amp;none</t>
+&amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
     </row>
@@ -11209,7 +11265,11 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B100" s="9" t="inlineStr"/>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_SHIFT</t>
+        </is>
+      </c>
       <c r="C100" s="9" t="inlineStr"/>
       <c r="D100" s="9" t="inlineStr"/>
       <c r="E100" s="9" t="inlineStr"/>
@@ -11221,7 +11281,11 @@
       <c r="K100" s="9" t="inlineStr"/>
       <c r="L100" s="9" t="inlineStr"/>
       <c r="M100" s="9" t="inlineStr"/>
-      <c r="N100" s="9" t="inlineStr"/>
+      <c r="N100" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RIGHT_SHIFT</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="6" t="inlineStr">
@@ -11238,13 +11302,13 @@
       <c r="C101" s="7" t="inlineStr">
         <is>
           <t>pos 35
-&amp;none</t>
+&amp;kp LEFT_WIN</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
           <t>pos 36
-&amp;none</t>
+&amp;kp LEFT_ALT</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
@@ -11295,8 +11359,16 @@
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr"/>
-      <c r="C102" s="9" t="inlineStr"/>
-      <c r="D102" s="9" t="inlineStr"/>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_WIN</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_ALT</t>
+        </is>
+      </c>
       <c r="E102" s="9" t="inlineStr"/>
       <c r="F102" s="9" t="inlineStr"/>
       <c r="G102" s="9" t="inlineStr"/>
@@ -11427,7 +11499,7 @@
       <c r="B106" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;none</t>
+&amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
@@ -11494,7 +11566,7 @@
       <c r="N106" s="7" t="inlineStr">
         <is>
           <t>pos 21
-&amp;none</t>
+&amp;kp RCTRL</t>
         </is>
       </c>
     </row>
@@ -11504,7 +11576,11 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B107" s="9" t="inlineStr"/>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LCTRL</t>
+        </is>
+      </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
           <t>&amp;mkp MB2</t>
@@ -11532,7 +11608,11 @@
           <t>&amp;mkp MB2</t>
         </is>
       </c>
-      <c r="N107" s="9" t="inlineStr"/>
+      <c r="N107" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RCTRL</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="6" t="inlineStr">
@@ -11543,7 +11623,7 @@
       <c r="B108" s="7" t="inlineStr">
         <is>
           <t>pos 22
-&amp;none</t>
+&amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
@@ -11610,7 +11690,7 @@
       <c r="N108" s="7" t="inlineStr">
         <is>
           <t>pos 33
-&amp;none</t>
+&amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
     </row>
@@ -11620,7 +11700,11 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B109" s="9" t="inlineStr"/>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_SHIFT</t>
+        </is>
+      </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
           <t>&amp;mkp MB5</t>
@@ -11648,7 +11732,11 @@
           <t>&amp;mkp MB5</t>
         </is>
       </c>
-      <c r="N109" s="9" t="inlineStr"/>
+      <c r="N109" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RIGHT_SHIFT</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="6" t="inlineStr">
@@ -11665,13 +11753,13 @@
       <c r="C110" s="7" t="inlineStr">
         <is>
           <t>pos 35
-&amp;none</t>
+&amp;kp LEFT_WIN</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
           <t>pos 36
-&amp;none</t>
+&amp;kp LEFT_ALT</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
@@ -11722,8 +11810,16 @@
         </is>
       </c>
       <c r="B111" s="9" t="inlineStr"/>
-      <c r="C111" s="9" t="inlineStr"/>
-      <c r="D111" s="9" t="inlineStr"/>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_WIN</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_ALT</t>
+        </is>
+      </c>
       <c r="E111" s="9" t="inlineStr"/>
       <c r="F111" s="9" t="inlineStr"/>
       <c r="G111" s="9" t="inlineStr"/>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -5388,7 +5388,7 @@
       <c r="B97" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;kp LCTRL</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
@@ -5455,7 +5455,7 @@
       <c r="N97" s="7" t="inlineStr">
         <is>
           <t>pos 21
-&amp;kp RCTRL</t>
+&amp;trans</t>
         </is>
       </c>
     </row>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>LCtrl</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr"/>
@@ -5491,7 +5491,7 @@
       <c r="M98" s="9" t="inlineStr"/>
       <c r="N98" s="9" t="inlineStr">
         <is>
-          <t>RCtrl</t>
+          <t>▽</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       <c r="B99" s="7" t="inlineStr">
         <is>
           <t>pos 22
-&amp;kp LEFT_SHIFT</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
@@ -5571,7 +5571,7 @@
       <c r="N99" s="7" t="inlineStr">
         <is>
           <t>pos 33
-&amp;kp RIGHT_SHIFT</t>
+&amp;trans</t>
         </is>
       </c>
     </row>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>LShift</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr"/>
@@ -5599,7 +5599,7 @@
       <c r="M100" s="9" t="inlineStr"/>
       <c r="N100" s="9" t="inlineStr">
         <is>
-          <t>RShift</t>
+          <t>▽</t>
         </is>
       </c>
     </row>
@@ -5618,13 +5618,13 @@
       <c r="C101" s="7" t="inlineStr">
         <is>
           <t>pos 35
-&amp;kp LEFT_WIN</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
           <t>pos 36
-&amp;kp LEFT_ALT</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
@@ -5677,12 +5677,12 @@
       <c r="B102" s="9" t="inlineStr"/>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>LWin</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>LAlt</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="E102" s="9" t="inlineStr"/>
@@ -11072,7 +11072,7 @@
       <c r="B97" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;kp LCTRL</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
@@ -11139,7 +11139,7 @@
       <c r="N97" s="7" t="inlineStr">
         <is>
           <t>pos 21
-&amp;kp RCTRL</t>
+&amp;trans</t>
         </is>
       </c>
     </row>
@@ -11151,7 +11151,7 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp LCTRL</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr"/>
@@ -11175,7 +11175,7 @@
       <c r="M98" s="9" t="inlineStr"/>
       <c r="N98" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp RCTRL</t>
+          <t>▽</t>
         </is>
       </c>
     </row>
@@ -11188,7 +11188,7 @@
       <c r="B99" s="7" t="inlineStr">
         <is>
           <t>pos 22
-&amp;kp LEFT_SHIFT</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
@@ -11255,7 +11255,7 @@
       <c r="N99" s="7" t="inlineStr">
         <is>
           <t>pos 33
-&amp;kp RIGHT_SHIFT</t>
+&amp;trans</t>
         </is>
       </c>
     </row>
@@ -11267,7 +11267,7 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp LEFT_SHIFT</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr"/>
@@ -11283,7 +11283,7 @@
       <c r="M100" s="9" t="inlineStr"/>
       <c r="N100" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp RIGHT_SHIFT</t>
+          <t>▽</t>
         </is>
       </c>
     </row>
@@ -11302,13 +11302,13 @@
       <c r="C101" s="7" t="inlineStr">
         <is>
           <t>pos 35
-&amp;kp LEFT_WIN</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
           <t>pos 36
-&amp;kp LEFT_ALT</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
@@ -11361,12 +11361,12 @@
       <c r="B102" s="9" t="inlineStr"/>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp LEFT_WIN</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp LEFT_ALT</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="E102" s="9" t="inlineStr"/>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -4546,7 +4546,7 @@
       <c r="B79" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;none</t>
+&amp;kp CAPSLOCK</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
@@ -4558,19 +4558,19 @@
       <c r="D79" s="7" t="inlineStr">
         <is>
           <t>pos 12
-&amp;none</t>
+&amp;kp PRINTSCREEN</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
           <t>pos 13
-&amp;none</t>
+&amp;kp SCROLLLOCK</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
           <t>pos 14
-&amp;none</t>
+&amp;kp PAUSE_BREAK</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
@@ -4613,7 +4613,7 @@
       <c r="N79" s="7" t="inlineStr">
         <is>
           <t>pos 21
-&amp;none</t>
+&amp;kp F11</t>
         </is>
       </c>
     </row>
@@ -4623,15 +4623,31 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B80" s="9" t="inlineStr"/>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>CAPSLOCK</t>
+        </is>
+      </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
           <t>リセット</t>
         </is>
       </c>
-      <c r="D80" s="9" t="inlineStr"/>
-      <c r="E80" s="9" t="inlineStr"/>
-      <c r="F80" s="9" t="inlineStr"/>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>PRINTSCREEN</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>SCROLLLOCK</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>PAUSE_BREAK</t>
+        </is>
+      </c>
       <c r="G80" s="9" t="inlineStr"/>
       <c r="H80" s="9" t="inlineStr"/>
       <c r="I80" s="9" t="inlineStr"/>
@@ -4643,7 +4659,11 @@
           <t>リセット</t>
         </is>
       </c>
-      <c r="N80" s="9" t="inlineStr"/>
+      <c r="N80" s="9" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
@@ -4654,7 +4674,7 @@
       <c r="B81" s="7" t="inlineStr">
         <is>
           <t>pos 22
-&amp;none</t>
+&amp;kp K_APP</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
@@ -4666,7 +4686,7 @@
       <c r="D81" s="7" t="inlineStr">
         <is>
           <t>pos 24
-&amp;none</t>
+&amp;kp INSERT</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
@@ -4721,7 +4741,7 @@
       <c r="N81" s="7" t="inlineStr">
         <is>
           <t>pos 33
-&amp;none</t>
+&amp;kp F12</t>
         </is>
       </c>
     </row>
@@ -4731,9 +4751,17 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B82" s="9" t="inlineStr"/>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>K_APP</t>
+        </is>
+      </c>
       <c r="C82" s="9" t="inlineStr"/>
-      <c r="D82" s="9" t="inlineStr"/>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
       <c r="E82" s="9" t="inlineStr"/>
       <c r="F82" s="9" t="inlineStr">
         <is>
@@ -4751,7 +4779,11 @@
       <c r="K82" s="9" t="inlineStr"/>
       <c r="L82" s="9" t="inlineStr"/>
       <c r="M82" s="9" t="inlineStr"/>
-      <c r="N82" s="9" t="inlineStr"/>
+      <c r="N82" s="9" t="inlineStr">
+        <is>
+          <t>F12</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
@@ -10230,7 +10262,7 @@
       <c r="B79" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;none</t>
+&amp;kp CAPSLOCK</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
@@ -10242,19 +10274,19 @@
       <c r="D79" s="7" t="inlineStr">
         <is>
           <t>pos 12
-&amp;none</t>
+&amp;kp PRINTSCREEN</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
           <t>pos 13
-&amp;none</t>
+&amp;kp SCROLLLOCK</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
           <t>pos 14
-&amp;none</t>
+&amp;kp PAUSE_BREAK</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
@@ -10297,7 +10329,7 @@
       <c r="N79" s="7" t="inlineStr">
         <is>
           <t>pos 21
-&amp;none</t>
+&amp;kp F11</t>
         </is>
       </c>
     </row>
@@ -10307,15 +10339,31 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B80" s="9" t="inlineStr"/>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp CAPSLOCK</t>
+        </is>
+      </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
           <t>&amp;sys_reset</t>
         </is>
       </c>
-      <c r="D80" s="9" t="inlineStr"/>
-      <c r="E80" s="9" t="inlineStr"/>
-      <c r="F80" s="9" t="inlineStr"/>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp PRINTSCREEN</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp SCROLLLOCK</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp PAUSE_BREAK</t>
+        </is>
+      </c>
       <c r="G80" s="9" t="inlineStr"/>
       <c r="H80" s="9" t="inlineStr"/>
       <c r="I80" s="9" t="inlineStr"/>
@@ -10327,7 +10375,11 @@
           <t>&amp;sys_reset</t>
         </is>
       </c>
-      <c r="N80" s="9" t="inlineStr"/>
+      <c r="N80" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp F11</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
@@ -10338,7 +10390,7 @@
       <c r="B81" s="7" t="inlineStr">
         <is>
           <t>pos 22
-&amp;none</t>
+&amp;kp K_APP</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
@@ -10350,7 +10402,7 @@
       <c r="D81" s="7" t="inlineStr">
         <is>
           <t>pos 24
-&amp;none</t>
+&amp;kp INSERT</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
@@ -10405,7 +10457,7 @@
       <c r="N81" s="7" t="inlineStr">
         <is>
           <t>pos 33
-&amp;none</t>
+&amp;kp F12</t>
         </is>
       </c>
     </row>
@@ -10415,9 +10467,17 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B82" s="9" t="inlineStr"/>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp K_APP</t>
+        </is>
+      </c>
       <c r="C82" s="9" t="inlineStr"/>
-      <c r="D82" s="9" t="inlineStr"/>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp INSERT</t>
+        </is>
+      </c>
       <c r="E82" s="9" t="inlineStr"/>
       <c r="F82" s="9" t="inlineStr">
         <is>
@@ -10435,7 +10495,11 @@
       <c r="K82" s="9" t="inlineStr"/>
       <c r="L82" s="9" t="inlineStr"/>
       <c r="M82" s="9" t="inlineStr"/>
-      <c r="N82" s="9" t="inlineStr"/>
+      <c r="N82" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp F12</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -4546,13 +4546,13 @@
       <c r="B79" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;kp CAPSLOCK</t>
+&amp;none</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
           <t>pos 11
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
@@ -4607,7 +4607,7 @@
       <c r="M79" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="N79" s="7" t="inlineStr">
@@ -4623,16 +4623,8 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B80" s="9" t="inlineStr">
-        <is>
-          <t>CAPSLOCK</t>
-        </is>
-      </c>
-      <c r="C80" s="9" t="inlineStr">
-        <is>
-          <t>リセット</t>
-        </is>
-      </c>
+      <c r="B80" s="9" t="inlineStr"/>
+      <c r="C80" s="9" t="inlineStr"/>
       <c r="D80" s="9" t="inlineStr">
         <is>
           <t>PRINTSCREEN</t>
@@ -4654,11 +4646,7 @@
       <c r="J80" s="9" t="inlineStr"/>
       <c r="K80" s="9" t="inlineStr"/>
       <c r="L80" s="9" t="inlineStr"/>
-      <c r="M80" s="9" t="inlineStr">
-        <is>
-          <t>リセット</t>
-        </is>
-      </c>
+      <c r="M80" s="9" t="inlineStr"/>
       <c r="N80" s="9" t="inlineStr">
         <is>
           <t>F11</t>
@@ -4698,7 +4686,7 @@
       <c r="F81" s="7" t="inlineStr">
         <is>
           <t>pos 26
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
@@ -4717,7 +4705,7 @@
       <c r="J81" s="7" t="inlineStr">
         <is>
           <t>pos 29
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="K81" s="7" t="inlineStr">
@@ -4763,19 +4751,11 @@
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr"/>
-      <c r="F82" s="9" t="inlineStr">
-        <is>
-          <t>ブートローダ</t>
-        </is>
-      </c>
+      <c r="F82" s="9" t="inlineStr"/>
       <c r="G82" s="9" t="inlineStr"/>
       <c r="H82" s="9" t="inlineStr"/>
       <c r="I82" s="9" t="inlineStr"/>
-      <c r="J82" s="9" t="inlineStr">
-        <is>
-          <t>ブートローダ</t>
-        </is>
-      </c>
+      <c r="J82" s="9" t="inlineStr"/>
       <c r="K82" s="9" t="inlineStr"/>
       <c r="L82" s="9" t="inlineStr"/>
       <c r="M82" s="9" t="inlineStr"/>
@@ -10262,13 +10242,13 @@
       <c r="B79" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;kp CAPSLOCK</t>
+&amp;none</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
           <t>pos 11
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
@@ -10323,7 +10303,7 @@
       <c r="M79" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="N79" s="7" t="inlineStr">
@@ -10339,16 +10319,8 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B80" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp CAPSLOCK</t>
-        </is>
-      </c>
-      <c r="C80" s="9" t="inlineStr">
-        <is>
-          <t>&amp;sys_reset</t>
-        </is>
-      </c>
+      <c r="B80" s="9" t="inlineStr"/>
+      <c r="C80" s="9" t="inlineStr"/>
       <c r="D80" s="9" t="inlineStr">
         <is>
           <t>&amp;kp PRINTSCREEN</t>
@@ -10370,11 +10342,7 @@
       <c r="J80" s="9" t="inlineStr"/>
       <c r="K80" s="9" t="inlineStr"/>
       <c r="L80" s="9" t="inlineStr"/>
-      <c r="M80" s="9" t="inlineStr">
-        <is>
-          <t>&amp;sys_reset</t>
-        </is>
-      </c>
+      <c r="M80" s="9" t="inlineStr"/>
       <c r="N80" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F11</t>
@@ -10414,7 +10382,7 @@
       <c r="F81" s="7" t="inlineStr">
         <is>
           <t>pos 26
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
@@ -10433,7 +10401,7 @@
       <c r="J81" s="7" t="inlineStr">
         <is>
           <t>pos 29
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="K81" s="7" t="inlineStr">
@@ -10479,19 +10447,11 @@
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr"/>
-      <c r="F82" s="9" t="inlineStr">
-        <is>
-          <t>&amp;bootloader</t>
-        </is>
-      </c>
+      <c r="F82" s="9" t="inlineStr"/>
       <c r="G82" s="9" t="inlineStr"/>
       <c r="H82" s="9" t="inlineStr"/>
       <c r="I82" s="9" t="inlineStr"/>
-      <c r="J82" s="9" t="inlineStr">
-        <is>
-          <t>&amp;bootloader</t>
-        </is>
-      </c>
+      <c r="J82" s="9" t="inlineStr"/>
       <c r="K82" s="9" t="inlineStr"/>
       <c r="L82" s="9" t="inlineStr"/>
       <c r="M82" s="9" t="inlineStr"/>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -4552,25 +4552,25 @@
       <c r="C79" s="7" t="inlineStr">
         <is>
           <t>pos 11
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
           <t>pos 12
-&amp;none</t>
+&amp;kp PRINTSCREEN</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
           <t>pos 13
-&amp;none</t>
+&amp;kp SCROLLLOCK</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
           <t>pos 14
-&amp;none</t>
+&amp;kp PAUSE_BREAK</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
@@ -4607,13 +4607,13 @@
       <c r="M79" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="N79" s="7" t="inlineStr">
         <is>
           <t>pos 21
-&amp;none</t>
+&amp;kp F11</t>
         </is>
       </c>
     </row>
@@ -4624,26 +4624,34 @@
         </is>
       </c>
       <c r="B80" s="9" t="inlineStr"/>
-      <c r="C80" s="9" t="inlineStr">
-        <is>
-          <t>リセット</t>
-        </is>
-      </c>
-      <c r="D80" s="9" t="inlineStr"/>
-      <c r="E80" s="9" t="inlineStr"/>
-      <c r="F80" s="9" t="inlineStr"/>
+      <c r="C80" s="9" t="inlineStr"/>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>PRINTSCREEN</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>SCROLLLOCK</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>PAUSE_BREAK</t>
+        </is>
+      </c>
       <c r="G80" s="9" t="inlineStr"/>
       <c r="H80" s="9" t="inlineStr"/>
       <c r="I80" s="9" t="inlineStr"/>
       <c r="J80" s="9" t="inlineStr"/>
       <c r="K80" s="9" t="inlineStr"/>
       <c r="L80" s="9" t="inlineStr"/>
-      <c r="M80" s="9" t="inlineStr">
-        <is>
-          <t>リセット</t>
-        </is>
-      </c>
-      <c r="N80" s="9" t="inlineStr"/>
+      <c r="M80" s="9" t="inlineStr"/>
+      <c r="N80" s="9" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
@@ -4654,7 +4662,7 @@
       <c r="B81" s="7" t="inlineStr">
         <is>
           <t>pos 22
-&amp;none</t>
+&amp;kp K_APP</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
@@ -4666,7 +4674,7 @@
       <c r="D81" s="7" t="inlineStr">
         <is>
           <t>pos 24
-&amp;none</t>
+&amp;kp INSERT</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
@@ -4678,7 +4686,7 @@
       <c r="F81" s="7" t="inlineStr">
         <is>
           <t>pos 26
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
@@ -4697,7 +4705,7 @@
       <c r="J81" s="7" t="inlineStr">
         <is>
           <t>pos 29
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="K81" s="7" t="inlineStr">
@@ -4721,7 +4729,7 @@
       <c r="N81" s="7" t="inlineStr">
         <is>
           <t>pos 33
-&amp;none</t>
+&amp;kp F12</t>
         </is>
       </c>
     </row>
@@ -4731,27 +4739,31 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B82" s="9" t="inlineStr"/>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>K_APP</t>
+        </is>
+      </c>
       <c r="C82" s="9" t="inlineStr"/>
-      <c r="D82" s="9" t="inlineStr"/>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
       <c r="E82" s="9" t="inlineStr"/>
-      <c r="F82" s="9" t="inlineStr">
-        <is>
-          <t>ブートローダ</t>
-        </is>
-      </c>
+      <c r="F82" s="9" t="inlineStr"/>
       <c r="G82" s="9" t="inlineStr"/>
       <c r="H82" s="9" t="inlineStr"/>
       <c r="I82" s="9" t="inlineStr"/>
-      <c r="J82" s="9" t="inlineStr">
-        <is>
-          <t>ブートローダ</t>
-        </is>
-      </c>
+      <c r="J82" s="9" t="inlineStr"/>
       <c r="K82" s="9" t="inlineStr"/>
       <c r="L82" s="9" t="inlineStr"/>
       <c r="M82" s="9" t="inlineStr"/>
-      <c r="N82" s="9" t="inlineStr"/>
+      <c r="N82" s="9" t="inlineStr">
+        <is>
+          <t>F12</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
@@ -10236,25 +10248,25 @@
       <c r="C79" s="7" t="inlineStr">
         <is>
           <t>pos 11
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
           <t>pos 12
-&amp;none</t>
+&amp;kp PRINTSCREEN</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
           <t>pos 13
-&amp;none</t>
+&amp;kp SCROLLLOCK</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
           <t>pos 14
-&amp;none</t>
+&amp;kp PAUSE_BREAK</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
@@ -10291,13 +10303,13 @@
       <c r="M79" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="N79" s="7" t="inlineStr">
         <is>
           <t>pos 21
-&amp;none</t>
+&amp;kp F11</t>
         </is>
       </c>
     </row>
@@ -10308,26 +10320,34 @@
         </is>
       </c>
       <c r="B80" s="9" t="inlineStr"/>
-      <c r="C80" s="9" t="inlineStr">
-        <is>
-          <t>&amp;sys_reset</t>
-        </is>
-      </c>
-      <c r="D80" s="9" t="inlineStr"/>
-      <c r="E80" s="9" t="inlineStr"/>
-      <c r="F80" s="9" t="inlineStr"/>
+      <c r="C80" s="9" t="inlineStr"/>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp PRINTSCREEN</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp SCROLLLOCK</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp PAUSE_BREAK</t>
+        </is>
+      </c>
       <c r="G80" s="9" t="inlineStr"/>
       <c r="H80" s="9" t="inlineStr"/>
       <c r="I80" s="9" t="inlineStr"/>
       <c r="J80" s="9" t="inlineStr"/>
       <c r="K80" s="9" t="inlineStr"/>
       <c r="L80" s="9" t="inlineStr"/>
-      <c r="M80" s="9" t="inlineStr">
-        <is>
-          <t>&amp;sys_reset</t>
-        </is>
-      </c>
-      <c r="N80" s="9" t="inlineStr"/>
+      <c r="M80" s="9" t="inlineStr"/>
+      <c r="N80" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp F11</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
@@ -10338,7 +10358,7 @@
       <c r="B81" s="7" t="inlineStr">
         <is>
           <t>pos 22
-&amp;none</t>
+&amp;kp K_APP</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
@@ -10350,7 +10370,7 @@
       <c r="D81" s="7" t="inlineStr">
         <is>
           <t>pos 24
-&amp;none</t>
+&amp;kp INSERT</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
@@ -10362,7 +10382,7 @@
       <c r="F81" s="7" t="inlineStr">
         <is>
           <t>pos 26
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
@@ -10381,7 +10401,7 @@
       <c r="J81" s="7" t="inlineStr">
         <is>
           <t>pos 29
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="K81" s="7" t="inlineStr">
@@ -10405,7 +10425,7 @@
       <c r="N81" s="7" t="inlineStr">
         <is>
           <t>pos 33
-&amp;none</t>
+&amp;kp F12</t>
         </is>
       </c>
     </row>
@@ -10415,27 +10435,31 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B82" s="9" t="inlineStr"/>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp K_APP</t>
+        </is>
+      </c>
       <c r="C82" s="9" t="inlineStr"/>
-      <c r="D82" s="9" t="inlineStr"/>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp INSERT</t>
+        </is>
+      </c>
       <c r="E82" s="9" t="inlineStr"/>
-      <c r="F82" s="9" t="inlineStr">
-        <is>
-          <t>&amp;bootloader</t>
-        </is>
-      </c>
+      <c r="F82" s="9" t="inlineStr"/>
       <c r="G82" s="9" t="inlineStr"/>
       <c r="H82" s="9" t="inlineStr"/>
       <c r="I82" s="9" t="inlineStr"/>
-      <c r="J82" s="9" t="inlineStr">
-        <is>
-          <t>&amp;bootloader</t>
-        </is>
-      </c>
+      <c r="J82" s="9" t="inlineStr"/>
       <c r="K82" s="9" t="inlineStr"/>
       <c r="L82" s="9" t="inlineStr"/>
       <c r="M82" s="9" t="inlineStr"/>
-      <c r="N82" s="9" t="inlineStr"/>
+      <c r="N82" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp F12</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
